--- a/misc/ipl/ipl_config.xlsx
+++ b/misc/ipl/ipl_config.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="IPL" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="97">
   <si>
     <t xml:space="preserve">Ref Des</t>
   </si>
@@ -46,7 +46,10 @@
     <t xml:space="preserve">Unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Step</t>
+    <t xml:space="preserve">Linstep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logstep</t>
   </si>
   <si>
     <t xml:space="preserve">Description</t>
@@ -118,7 +121,7 @@
     <t xml:space="preserve">R164</t>
   </si>
   <si>
-    <t xml:space="preserve">Rpd</t>
+    <t xml:space="preserve">Rdg</t>
   </si>
   <si>
     <t xml:space="preserve">C127</t>
@@ -296,6 +299,9 @@
   </si>
   <si>
     <t xml:space="preserve">Input voltage range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fplot</t>
   </si>
   <si>
     <t xml:space="preserve">DEBUG</t>
@@ -442,14 +448,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="3" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="9.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="29.76"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="29.76"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -480,57 +487,63 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1.8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>499</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1.8</v>
@@ -539,126 +552,138 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>499</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1.8</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>499</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1.8</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1.8</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>300</v>
+        <v>249</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1.8</v>
@@ -667,222 +692,243 @@
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1.8</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>3.32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1.8</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1.8</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>100</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>100</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>35</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>3</v>
@@ -891,21 +937,24 @@
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>2.462</v>
@@ -917,219 +966,240 @@
         <v>2.538</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>500</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>52</v>
+        <v>13</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>20</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>56</v>
+        <v>13</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>20</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>20</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>59</v>
+        <v>13</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>450</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>61</v>
+        <v>13</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>86</v>
@@ -1141,59 +1211,65 @@
         <v>110</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>70</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>67</v>
+        <v>13</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>16</v>
@@ -1205,228 +1281,249 @@
         <v>25</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>72</v>
+        <v>13</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>80</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>74</v>
+        <v>13</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>76</v>
+        <v>13</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>79</v>
+        <v>13</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>56</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>82</v>
+        <v>13</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>100</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>82</v>
+        <v>13</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>12</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>5</v>
@@ -1435,21 +1532,24 @@
         <v>1</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>75</v>
@@ -1461,27 +1561,30 @@
         <v>91</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>88</v>
+        <v>13</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>8.5</v>
@@ -1493,51 +1596,90 @@
         <v>60</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="J33" s="5" t="s">
-        <v>91</v>
+      <c r="J33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="A34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>12</v>
+      <c r="C34" s="2" t="n">
+        <v>0.0001</v>
       </c>
       <c r="D34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="2" t="n">
+      <c r="E35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>94</v>
+      <c r="H35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/misc/ipl/ipl_config.xlsx
+++ b/misc/ipl/ipl_config.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="100">
   <si>
     <t xml:space="preserve">Ref Des</t>
   </si>
@@ -298,10 +298,19 @@
     <t xml:space="preserve">Vcg</t>
   </si>
   <si>
-    <t xml:space="preserve">Input voltage range</t>
+    <t xml:space="preserve">Input voltage range, Linstep is resolution to step from min to max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vin</t>
   </si>
   <si>
     <t xml:space="preserve">Fplot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plot frequency range. 1/Logstep is number of points per decade</t>
   </si>
   <si>
     <t xml:space="preserve">DEBUG</t>
@@ -448,7 +457,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.53"/>
@@ -1616,70 +1625,102 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="2" t="n">
         <v>0.0001</v>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E35" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="F35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K34" s="5"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="2" t="n">
+      <c r="I35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="2" t="n">
+      <c r="E36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>96</v>
+      <c r="H36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
